--- a/data/mapas/Mapa_de_Carrera_Quimica.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Quimica.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B46, "SI")</f>
+        <f>COUNTIF(B6:B44, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C46, "SI")</f>
+        <f>COUNTIF(C6:C44, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F46, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F44, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>INTRODUCCION A LA Química</t>
+          <t>Química General e Inorgánica I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B46, "SI")/35</f>
+        <f>COUNTIF(B6:B44, "SI")/35</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Mecanica y Optica Geometrica</t>
+          <t>Laboratorio de Química General</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C46, "SI")/35</f>
+        <f>COUNTIF(C6:C44, "SI")/35</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Química GENERAL E INORGANICA I</t>
+          <t>Matemática I (Cálculo y Álgebra)</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -791,11 +791,38 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Física I</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E9" s="10">
+        <f>IF(B9="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F9" s="10">
+        <f>IF(C9="SI", "APROBADO", IF(B9="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="11">
+        <f>IF(C9="SI", "🟢 Aprobada", IF(B9="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -806,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -821,7 +848,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E10" s="10">
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -921,49 +948,49 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Práctica Docente II</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>4. Las columnas E, F y G se actualizan automaticamente en tiempo real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Química General e Inorgánica II</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>2° Año</t>
         </is>
       </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>4. Las columnas E, F y G se actualizan automaticamente en tiempo real.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="E14" s="10">
+        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F14" s="10">
+        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -974,7 +1001,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Química Orgánica I</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -989,7 +1016,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E15" s="10">
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Química Analítica Cualitativa</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Matemática II</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Física II</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1112,17 +1139,44 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Didáctica General</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E19" s="10">
+        <f>IF(B19="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>IF(C19="SI", "APROBADO", IF(B19="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G19" s="11">
+        <f>IF(C19="SI", "🟢 Aprobada", IF(B19="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1137,7 +1191,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E20" s="10">
@@ -1156,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Sujetos de la Educación</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1190,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Investigación Educativa</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1205,7 +1259,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E22" s="10">
@@ -1221,51 +1275,51 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Práctica Docente IV</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E23" s="10">
-        <f>IF(B23="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>IF(C23="SI", "APROBADO", IF(B23="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G23" s="11">
-        <f>IF(C23="SI", "🟢 Aprobada", IF(B23="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Química Orgánica II</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E24" s="10">
+        <f>IF(B24="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>IF(C24="SI", "APROBADO", IF(B24="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
+        <f>IF(C24="SI", "🟢 Aprobada", IF(B24="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Química Analítica Cuantitativa e Instrumental</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1280,7 +1334,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1299,7 +1353,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Fisicoquímica I</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Didáctica de la Química I</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Biología Celular y Bioquímica</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1398,17 +1452,44 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Historia Social de la Educación</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E29" s="10">
+        <f>IF(B29="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F29" s="10">
+        <f>IF(C29="SI", "APROBADO", IF(B29="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
+        <f>IF(C29="SI", "🟢 Aprobada", IF(B29="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior II</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1423,7 +1504,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E30" s="10">
@@ -1442,7 +1523,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Construcción de la Práctica Docente I</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1457,7 +1538,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1473,44 +1554,17 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Práctica de Nivel Superior II</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E32" s="10">
-        <f>IF(B32="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F32" s="10">
-        <f>IF(C32="SI", "APROBADO", IF(B32="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G32" s="11">
-        <f>IF(C32="SI", "🟢 Aprobada", IF(B32="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Fisicoquímica II</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1541,17 +1595,44 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Química Industrial y Ambiental</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E34" s="10">
+        <f>IF(B34="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>IF(C34="SI", "APROBADO", IF(B34="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="11">
+        <f>IF(C34="SI", "🟢 Aprobada", IF(B34="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Análisis MATEMATICO II</t>
+          <t>Bromatología y Toxicología</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1566,7 +1647,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1585,7 +1666,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Biología CELULAR (1º cuat)</t>
+          <t>Didáctica de la Química II</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1600,7 +1681,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1619,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Calor y Termodinamica</t>
+          <t>Historia y Epistemología de la Química</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1634,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1653,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Dinamica Terrestre</t>
+          <t>Educación Sexual Integral (ESI)</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1668,7 +1749,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E38" s="10">
@@ -1687,7 +1768,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1702,7 +1783,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1721,7 +1802,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Química ANALITICA</t>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1736,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1752,44 +1833,17 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>Química BIOLOGICA</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E41" s="10">
-        <f>IF(B41="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F41" s="10">
-        <f>IF(C41="SI", "APROBADO", IF(B41="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G41" s="11">
-        <f>IF(C41="SI", "🟢 Aprobada", IF(B41="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Química Física</t>
+          <t>Seminario de Química Aplicada</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1804,7 +1858,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1823,7 +1877,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Química GENERAL E INORGANICA II</t>
+          <t>Taller de Seguridad e Higiene en Laboratorio</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1838,7 +1892,7 @@
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E43" s="10">
@@ -1857,7 +1911,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>SEMINARIO DIDACTICO DISCIPLINAR DE Química</t>
+          <t>Taller de Investigación en Enseñanza de la Química</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -1872,7 +1926,7 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>General / Optativas</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E44" s="10">
@@ -1888,96 +1942,26 @@
         <v/>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>SISTEMA Y Política Educativa</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo de Campo II</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A14:G14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A9:G9"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A34:G34"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B10 B11 B12 B13 B15 B16 B17 B18 B20 B21 B22 B23 B25 B26 B27 B28 B30 B31 B32 B33 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 C6 C7 C8 C10 C11 C12 C13 C15 C16 C17 C18 C20 C21 C22 C23 C25 C26 C27 C28 C30 C31 C32 C33 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B22 B24 B25 B26 B27 B28 B29 B30 B31 B33 B34 B35 B36 B37 B38 B39 B40 B42 B43 B44 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C22 C24 C25 C26 C27 C28 C29 C30 C31 C33 C34 C35 C36 C37 C38 C39 C40 C42 C43 C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Quimica.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Quimica.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B44, "SI")</f>
+        <f>COUNTIF(B6:B51, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C44, "SI")</f>
+        <f>COUNTIF(C6:C51, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F44, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F51, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Química General e Inorgánica I</t>
+          <t>Análisis Matemático I</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B44, "SI")/35</f>
+        <f>COUNTIF(B6:B51, "SI")/41</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Laboratorio de Química General</t>
+          <t>Mecánica y óptica geométrica</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C44, "SI")/35</f>
+        <f>COUNTIF(C6:C51, "SI")/41</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Matemática I (Cálculo y Álgebra)</t>
+          <t>Introducción a la química</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Física I</t>
+          <t>Química general e inorgánica 1</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Sujetos de nivel</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Psicología educacional</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Lectura, escritura y oralidad 1</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Química General e Inorgánica II</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -999,37 +1026,10 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Química Orgánica I</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E15" s="10">
-        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
-        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G15" s="11">
-        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Química Analítica Cualitativa</t>
+          <t>Análisis Matemático II</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Matemática II</t>
+          <t>Electromagnetismo y fenomenos ondulatorios</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Física II</t>
+          <t>Introducción a la dinámica terrestre y mineralogía</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Química general e inorgánica 2</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Química orgánica 1</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Didáctica general</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1275,51 +1275,51 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>DDHH, sociedad y estado</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E23" s="10">
+        <f>IF(B23="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>IF(C23="SI", "APROBADO", IF(B23="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
+        <f>IF(C23="SI", "🟢 Aprobada", IF(B23="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>📌 3° AÑO</t>
         </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>Química Orgánica II</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E24" s="10">
-        <f>IF(B24="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F24" s="10">
-        <f>IF(C24="SI", "APROBADO", IF(B24="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G24" s="11">
-        <f>IF(C24="SI", "🟢 Aprobada", IF(B24="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Química Analítica Cuantitativa e Instrumental</t>
+          <t>Matemática aplicada</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Fisicoquímica I</t>
+          <t>Calor y termodinámica</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Química I</t>
+          <t>Dinamica terrestre</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Biología Celular y Bioquímica</t>
+          <t>Química orgánica 2</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Química analitica</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Biología celular</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -1523,7 +1523,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente I</t>
+          <t>Fisiologia celular y humana</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1554,17 +1554,44 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la practica docente 1</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E32" s="10">
+        <f>IF(B32="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f>IF(C32="SI", "APROBADO", IF(B32="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G32" s="11">
+        <f>IF(C32="SI", "🟢 Aprobada", IF(B32="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Fisicoquímica II</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Química Industrial y Ambiental</t>
+          <t>Esi</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1629,44 +1656,17 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Bromatología y Toxicología</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E35" s="10">
-        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
-        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G35" s="11">
-        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>📌 4° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Química II</t>
+          <t>Química física</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1700,7 +1700,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Historia y Epistemología de la Química</t>
+          <t>Intoducción a la química industrial</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Química industrial descriptiva</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Química biológica</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Epistemología e historia de la química</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1843,7 +1843,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Química Aplicada</t>
+          <t>Lectura, escritura y oralidad 2</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1877,7 +1877,7 @@
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>Taller de Seguridad e Higiene en Laboratorio</t>
+          <t>Sistema y política educativa</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación en Enseñanza de la Química</t>
+          <t>Historia de la educación Argentina</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -1942,26 +1942,238 @@
         <v/>
       </c>
     </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Biología molecular</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Biotecnologia</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Metodologia de la investigación</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Nuevas tecnologias</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Lengua extranjera</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la practica docente 2</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E51" s="10">
+        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A13:G13"/>
+  <mergeCells count="16">
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:G15"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B22 B24 B25 B26 B27 B28 B29 B30 B31 B33 B34 B35 B36 B37 B38 B39 B40 B42 B43 B44 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C22 C24 C25 C26 C27 C28 C29 C30 C31 C33 C34 C35 C36 C37 C38 C39 C40 C42 C43 C44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B16 B17 B18 B19 B20 B21 B22 B23 B25 B26 B27 B28 B29 B30 B31 B32 B33 B34 B36 B37 B38 B39 B40 B42 B43 B44 B46 B47 B48 B49 B50 B51 C6 C7 C8 C9 C10 C11 C12 C13 C14 C16 C17 C18 C19 C20 C21 C22 C23 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C36 C37 C38 C39 C40 C42 C43 C44 C46 C47 C48 C49 C50 C51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
